--- a/data/numeric/input/old_data_50/工作簿2_更新.xlsx
+++ b/data/numeric/input/old_data_50/工作簿2_更新.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="320">
   <si>
     <t>报告：成功合并 12 个工作表，共 15583 行数据。</t>
   </si>
@@ -445,9 +445,6 @@
   </si>
   <si>
     <t>20.95</t>
-  </si>
-  <si>
-    <t>张春梅</t>
   </si>
   <si>
     <t>0.840416666666667</t>
@@ -1003,14 +1000,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1466,148 +1456,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2762,19 +2752,17 @@
       <c r="L13" t="s">
         <v>138</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13"/>
+      <c r="N13" t="s">
         <v>139</v>
       </c>
-      <c r="N13" t="s">
+      <c r="O13" t="s">
         <v>140</v>
-      </c>
-      <c r="O13" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B14" t="s">
         <v>47</v>
@@ -2786,42 +2774,42 @@
         <v>49</v>
       </c>
       <c r="E14" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" t="s">
         <v>143</v>
       </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>144</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>145</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>146</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>147</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>148</v>
-      </c>
-      <c r="O14" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
@@ -2833,7 +2821,7 @@
         <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F15" t="s">
         <v>51</v>
@@ -2851,24 +2839,24 @@
         <v>128</v>
       </c>
       <c r="K15" t="s">
+        <v>151</v>
+      </c>
+      <c r="L15" t="s">
         <v>152</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>153</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>154</v>
       </c>
-      <c r="N15" t="s">
+      <c r="O15" t="s">
         <v>155</v>
-      </c>
-      <c r="O15" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
@@ -2880,42 +2868,42 @@
         <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F16" t="s">
         <v>52</v>
       </c>
       <c r="G16" t="s">
+        <v>158</v>
+      </c>
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" t="s">
         <v>159</v>
       </c>
-      <c r="H16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" t="s">
-        <v>51</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>160</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>161</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>162</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>163</v>
       </c>
-      <c r="N16" t="s">
+      <c r="O16" t="s">
         <v>164</v>
-      </c>
-      <c r="O16" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
@@ -2927,7 +2915,7 @@
         <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F17" t="s">
         <v>51</v>
@@ -2945,24 +2933,24 @@
         <v>136</v>
       </c>
       <c r="K17" t="s">
+        <v>167</v>
+      </c>
+      <c r="L17" t="s">
         <v>168</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>169</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>170</v>
       </c>
-      <c r="N17" t="s">
+      <c r="O17" t="s">
         <v>171</v>
-      </c>
-      <c r="O17" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
@@ -2974,42 +2962,42 @@
         <v>49</v>
       </c>
       <c r="E18" t="s">
+        <v>173</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" t="s">
         <v>174</v>
       </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>175</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>176</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>177</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" t="s">
         <v>178</v>
       </c>
-      <c r="L18" t="s">
+      <c r="M18" t="s">
         <v>179</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>180</v>
       </c>
-      <c r="N18" t="s">
+      <c r="O18" t="s">
         <v>181</v>
-      </c>
-      <c r="O18" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -3021,7 +3009,7 @@
         <v>49</v>
       </c>
       <c r="E19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F19" t="s">
         <v>51</v>
@@ -3039,24 +3027,24 @@
         <v>101</v>
       </c>
       <c r="K19" t="s">
+        <v>184</v>
+      </c>
+      <c r="L19" t="s">
         <v>185</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>186</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>187</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>188</v>
-      </c>
-      <c r="O19" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
@@ -3068,42 +3056,42 @@
         <v>49</v>
       </c>
       <c r="E20" t="s">
+        <v>190</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J20" t="s">
         <v>191</v>
       </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H20" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
+        <v>184</v>
+      </c>
+      <c r="L20" t="s">
         <v>192</v>
       </c>
-      <c r="K20" t="s">
-        <v>185</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="M20" t="s">
         <v>193</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
+        <v>187</v>
+      </c>
+      <c r="O20" t="s">
         <v>194</v>
-      </c>
-      <c r="N20" t="s">
-        <v>188</v>
-      </c>
-      <c r="O20" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
@@ -3115,42 +3103,42 @@
         <v>49</v>
       </c>
       <c r="E21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" t="s">
+        <v>51</v>
+      </c>
+      <c r="H21" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" t="s">
         <v>197</v>
       </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" t="s">
-        <v>51</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>198</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>199</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M21" t="s">
         <v>200</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>201</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>202</v>
-      </c>
-      <c r="O21" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:15">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B22" t="s">
         <v>47</v>
@@ -3162,42 +3150,42 @@
         <v>49</v>
       </c>
       <c r="E22" t="s">
+        <v>204</v>
+      </c>
+      <c r="F22" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" t="s">
         <v>205</v>
       </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
+        <v>51</v>
+      </c>
+      <c r="J22" t="s">
+        <v>197</v>
+      </c>
+      <c r="K22" t="s">
+        <v>191</v>
+      </c>
+      <c r="L22" t="s">
         <v>206</v>
       </c>
-      <c r="I22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" t="s">
-        <v>198</v>
-      </c>
-      <c r="K22" t="s">
-        <v>192</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="M22" t="s">
         <v>207</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>208</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>209</v>
-      </c>
-      <c r="O22" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -3209,42 +3197,42 @@
         <v>49</v>
       </c>
       <c r="E23" t="s">
+        <v>211</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" t="s">
+        <v>51</v>
+      </c>
+      <c r="I23" t="s">
+        <v>51</v>
+      </c>
+      <c r="J23" t="s">
         <v>212</v>
       </c>
-      <c r="F23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" t="s">
-        <v>51</v>
-      </c>
-      <c r="H23" t="s">
-        <v>51</v>
-      </c>
-      <c r="I23" t="s">
-        <v>51</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>213</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" t="s">
         <v>214</v>
       </c>
-      <c r="L23" t="s">
+      <c r="M23" t="s">
         <v>215</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>216</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>217</v>
-      </c>
-      <c r="O23" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:15">
       <c r="A24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -3256,42 +3244,42 @@
         <v>49</v>
       </c>
       <c r="E24" t="s">
+        <v>219</v>
+      </c>
+      <c r="F24" t="s">
+        <v>51</v>
+      </c>
+      <c r="G24" t="s">
+        <v>51</v>
+      </c>
+      <c r="H24" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" t="s">
+        <v>176</v>
+      </c>
+      <c r="K24" t="s">
+        <v>198</v>
+      </c>
+      <c r="L24" t="s">
         <v>220</v>
       </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I24" t="s">
-        <v>51</v>
-      </c>
-      <c r="J24" t="s">
-        <v>177</v>
-      </c>
-      <c r="K24" t="s">
-        <v>199</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="M24" t="s">
         <v>221</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
+        <v>201</v>
+      </c>
+      <c r="O24" t="s">
         <v>222</v>
-      </c>
-      <c r="N24" t="s">
-        <v>202</v>
-      </c>
-      <c r="O24" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
@@ -3318,27 +3306,27 @@
         <v>51</v>
       </c>
       <c r="J25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s">
         <v>72</v>
       </c>
       <c r="N25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -3350,7 +3338,7 @@
         <v>49</v>
       </c>
       <c r="E26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F26" t="s">
         <v>51</v>
@@ -3368,24 +3356,24 @@
         <v>78</v>
       </c>
       <c r="K26" t="s">
+        <v>228</v>
+      </c>
+      <c r="L26" t="s">
         <v>229</v>
       </c>
-      <c r="L26" t="s">
+      <c r="M26" t="s">
         <v>230</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>231</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>232</v>
-      </c>
-      <c r="O26" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -3432,7 +3420,7 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -3444,42 +3432,42 @@
         <v>49</v>
       </c>
       <c r="E28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" t="s">
+        <v>51</v>
+      </c>
+      <c r="H28" t="s">
+        <v>51</v>
+      </c>
+      <c r="I28" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28" t="s">
         <v>236</v>
       </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28" t="s">
-        <v>51</v>
-      </c>
-      <c r="H28" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>237</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" t="s">
         <v>238</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>239</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>240</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>241</v>
-      </c>
-      <c r="O28" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -3491,7 +3479,7 @@
         <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F29" t="s">
         <v>51</v>
@@ -3509,24 +3497,24 @@
         <v>101</v>
       </c>
       <c r="K29" t="s">
+        <v>244</v>
+      </c>
+      <c r="L29" t="s">
         <v>245</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M29" t="s">
         <v>246</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N29" t="s">
         <v>247</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>248</v>
-      </c>
-      <c r="O29" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
@@ -3538,7 +3526,7 @@
         <v>49</v>
       </c>
       <c r="E30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F30" t="s">
         <v>51</v>
@@ -3556,24 +3544,24 @@
         <v>101</v>
       </c>
       <c r="K30" t="s">
+        <v>251</v>
+      </c>
+      <c r="L30" t="s">
         <v>252</v>
       </c>
-      <c r="L30" t="s">
+      <c r="M30" t="s">
         <v>253</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" t="s">
         <v>254</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>255</v>
-      </c>
-      <c r="O30" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -3585,7 +3573,7 @@
         <v>49</v>
       </c>
       <c r="E31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F31" t="s">
         <v>51</v>
@@ -3603,24 +3591,24 @@
         <v>85</v>
       </c>
       <c r="K31" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L31" t="s">
+        <v>258</v>
+      </c>
+      <c r="M31" t="s">
         <v>259</v>
       </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
+        <v>187</v>
+      </c>
+      <c r="O31" t="s">
         <v>260</v>
-      </c>
-      <c r="N31" t="s">
-        <v>188</v>
-      </c>
-      <c r="O31" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -3643,7 +3631,7 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -3655,7 +3643,7 @@
         <v>49</v>
       </c>
       <c r="E33" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F33" t="s">
         <v>51</v>
@@ -3676,21 +3664,21 @@
         <v>78</v>
       </c>
       <c r="L33" t="s">
+        <v>263</v>
+      </c>
+      <c r="M33" t="s">
         <v>264</v>
-      </c>
-      <c r="M33" t="s">
-        <v>265</v>
       </c>
       <c r="N33" t="s">
         <v>81</v>
       </c>
       <c r="O33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
@@ -3702,42 +3690,42 @@
         <v>49</v>
       </c>
       <c r="E34" t="s">
+        <v>267</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" t="s">
+        <v>51</v>
+      </c>
+      <c r="I34" t="s">
+        <v>51</v>
+      </c>
+      <c r="J34" t="s">
         <v>268</v>
       </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34" t="s">
-        <v>51</v>
-      </c>
-      <c r="H34" t="s">
-        <v>51</v>
-      </c>
-      <c r="I34" t="s">
-        <v>51</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>269</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>270</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M34" t="s">
         <v>271</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N34" t="s">
         <v>272</v>
       </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>273</v>
-      </c>
-      <c r="O34" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s">
         <v>47</v>
@@ -3749,42 +3737,42 @@
         <v>49</v>
       </c>
       <c r="E35" t="s">
+        <v>275</v>
+      </c>
+      <c r="F35" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" t="s">
+        <v>51</v>
+      </c>
+      <c r="I35" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" t="s">
+        <v>268</v>
+      </c>
+      <c r="K35" t="s">
         <v>276</v>
       </c>
-      <c r="F35" t="s">
-        <v>51</v>
-      </c>
-      <c r="G35" t="s">
-        <v>51</v>
-      </c>
-      <c r="H35" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35" t="s">
-        <v>51</v>
-      </c>
-      <c r="J35" t="s">
-        <v>269</v>
-      </c>
-      <c r="K35" t="s">
+      <c r="L35" t="s">
         <v>277</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
         <v>278</v>
       </c>
-      <c r="M35" t="s">
+      <c r="N35" t="s">
         <v>279</v>
       </c>
-      <c r="N35" t="s">
+      <c r="O35" t="s">
         <v>280</v>
-      </c>
-      <c r="O35" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s">
         <v>47</v>
@@ -3796,42 +3784,42 @@
         <v>49</v>
       </c>
       <c r="E36" t="s">
+        <v>282</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" t="s">
+        <v>51</v>
+      </c>
+      <c r="I36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" t="s">
+        <v>159</v>
+      </c>
+      <c r="K36" t="s">
+        <v>167</v>
+      </c>
+      <c r="L36" t="s">
         <v>283</v>
       </c>
-      <c r="F36" t="s">
-        <v>51</v>
-      </c>
-      <c r="G36" t="s">
-        <v>51</v>
-      </c>
-      <c r="H36" t="s">
-        <v>51</v>
-      </c>
-      <c r="I36" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36" t="s">
-        <v>160</v>
-      </c>
-      <c r="K36" t="s">
-        <v>168</v>
-      </c>
-      <c r="L36" t="s">
+      <c r="M36" t="s">
         <v>284</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
+        <v>170</v>
+      </c>
+      <c r="O36" t="s">
         <v>285</v>
-      </c>
-      <c r="N36" t="s">
-        <v>171</v>
-      </c>
-      <c r="O36" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
@@ -3843,42 +3831,42 @@
         <v>49</v>
       </c>
       <c r="E37" t="s">
+        <v>287</v>
+      </c>
+      <c r="F37" t="s">
+        <v>51</v>
+      </c>
+      <c r="G37" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" t="s">
+        <v>51</v>
+      </c>
+      <c r="I37" t="s">
+        <v>51</v>
+      </c>
+      <c r="J37" t="s">
+        <v>176</v>
+      </c>
+      <c r="K37" t="s">
         <v>288</v>
       </c>
-      <c r="F37" t="s">
-        <v>51</v>
-      </c>
-      <c r="G37" t="s">
-        <v>51</v>
-      </c>
-      <c r="H37" t="s">
-        <v>51</v>
-      </c>
-      <c r="I37" t="s">
-        <v>51</v>
-      </c>
-      <c r="J37" t="s">
-        <v>177</v>
-      </c>
-      <c r="K37" t="s">
+      <c r="L37" t="s">
         <v>289</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>290</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
+        <v>176</v>
+      </c>
+      <c r="O37" t="s">
         <v>291</v>
-      </c>
-      <c r="N37" t="s">
-        <v>177</v>
-      </c>
-      <c r="O37" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="38" spans="1:15">
       <c r="A38" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s">
         <v>47</v>
@@ -3890,42 +3878,42 @@
         <v>49</v>
       </c>
       <c r="E38" t="s">
+        <v>293</v>
+      </c>
+      <c r="F38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" t="s">
+        <v>51</v>
+      </c>
+      <c r="H38" t="s">
+        <v>51</v>
+      </c>
+      <c r="I38" t="s">
+        <v>51</v>
+      </c>
+      <c r="J38" t="s">
+        <v>197</v>
+      </c>
+      <c r="K38" t="s">
         <v>294</v>
       </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-      <c r="G38" t="s">
-        <v>51</v>
-      </c>
-      <c r="H38" t="s">
-        <v>51</v>
-      </c>
-      <c r="I38" t="s">
-        <v>51</v>
-      </c>
-      <c r="J38" t="s">
-        <v>198</v>
-      </c>
-      <c r="K38" t="s">
+      <c r="L38" t="s">
         <v>295</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>296</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>297</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>298</v>
-      </c>
-      <c r="O38" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:15">
       <c r="A39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s">
         <v>47</v>
@@ -3937,7 +3925,7 @@
         <v>49</v>
       </c>
       <c r="E39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F39" t="s">
         <v>51</v>
@@ -3955,24 +3943,24 @@
         <v>62</v>
       </c>
       <c r="K39" t="s">
+        <v>301</v>
+      </c>
+      <c r="L39" t="s">
         <v>302</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>303</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>304</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" t="s">
         <v>305</v>
-      </c>
-      <c r="O39" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:15">
       <c r="A40" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
@@ -3984,42 +3972,42 @@
         <v>49</v>
       </c>
       <c r="E40" t="s">
+        <v>307</v>
+      </c>
+      <c r="F40" t="s">
+        <v>51</v>
+      </c>
+      <c r="G40" t="s">
+        <v>51</v>
+      </c>
+      <c r="H40" t="s">
+        <v>51</v>
+      </c>
+      <c r="I40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J40" t="s">
+        <v>176</v>
+      </c>
+      <c r="K40" t="s">
         <v>308</v>
       </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-      <c r="G40" t="s">
-        <v>51</v>
-      </c>
-      <c r="H40" t="s">
-        <v>51</v>
-      </c>
-      <c r="I40" t="s">
-        <v>51</v>
-      </c>
-      <c r="J40" t="s">
-        <v>177</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>309</v>
       </c>
-      <c r="L40" t="s">
+      <c r="M40" t="s">
         <v>310</v>
       </c>
-      <c r="M40" t="s">
+      <c r="N40" t="s">
         <v>311</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>312</v>
-      </c>
-      <c r="O40" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="41" spans="1:15">
       <c r="A41" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -4031,37 +4019,37 @@
         <v>49</v>
       </c>
       <c r="E41" t="s">
+        <v>314</v>
+      </c>
+      <c r="F41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41" t="s">
+        <v>51</v>
+      </c>
+      <c r="H41" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" t="s">
+        <v>51</v>
+      </c>
+      <c r="J41" t="s">
+        <v>191</v>
+      </c>
+      <c r="K41" t="s">
         <v>315</v>
       </c>
-      <c r="F41" t="s">
-        <v>51</v>
-      </c>
-      <c r="G41" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41" t="s">
-        <v>51</v>
-      </c>
-      <c r="I41" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" t="s">
-        <v>192</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="L41" t="s">
         <v>316</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>317</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>318</v>
       </c>
-      <c r="N41" t="s">
+      <c r="O41" t="s">
         <v>319</v>
-      </c>
-      <c r="O41" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4234,13 +4222,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4797D602-B4AB-43D6-A671-F8E5425ECB4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3536C45E-EF8F-40AE-B95F-6F9034BEC638}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2783F52B-02F1-4D51-BFD1-0CF571FF48DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAD775D0-7A12-44B5-A860-11B78F2CC16B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49ED66A3-E5AC-4FEF-A8B7-765991E94140}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{514B0205-3735-4CA0-BEB1-DD9170D1CF8E}"/>
 </file>